--- a/artfynd/S 1387-2022 artfynd.xlsx
+++ b/artfynd/S 1387-2022 artfynd.xlsx
@@ -2357,7 +2357,7 @@
         <v>132665500</v>
       </c>
       <c r="B16" t="n">
-        <v>58136</v>
+        <v>58169</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>132665513</v>
       </c>
       <c r="B17" t="n">
-        <v>58136</v>
+        <v>58169</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/S 1387-2022 artfynd.xlsx
+++ b/artfynd/S 1387-2022 artfynd.xlsx
@@ -2357,7 +2357,7 @@
         <v>132665500</v>
       </c>
       <c r="B16" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>132665513</v>
       </c>
       <c r="B17" t="n">
-        <v>58169</v>
+        <v>58182</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/S 1387-2022 artfynd.xlsx
+++ b/artfynd/S 1387-2022 artfynd.xlsx
@@ -2357,7 +2357,7 @@
         <v>132665500</v>
       </c>
       <c r="B16" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2481,7 +2481,7 @@
         <v>132665513</v>
       </c>
       <c r="B17" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/S 1387-2022 artfynd.xlsx
+++ b/artfynd/S 1387-2022 artfynd.xlsx
@@ -2389,11 +2389,7 @@
       </c>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2513,11 +2509,7 @@
       </c>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>spel/sång</t>
-        </is>
-      </c>
+      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>

--- a/artfynd/S 1387-2022 artfynd.xlsx
+++ b/artfynd/S 1387-2022 artfynd.xlsx
@@ -2357,7 +2357,7 @@
         <v>132665500</v>
       </c>
       <c r="B16" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>132665513</v>
       </c>
       <c r="B17" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/S 1387-2022 artfynd.xlsx
+++ b/artfynd/S 1387-2022 artfynd.xlsx
@@ -2357,7 +2357,7 @@
         <v>132665500</v>
       </c>
       <c r="B16" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>132665513</v>
       </c>
       <c r="B17" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/S 1387-2022 artfynd.xlsx
+++ b/artfynd/S 1387-2022 artfynd.xlsx
@@ -2357,7 +2357,7 @@
         <v>132665500</v>
       </c>
       <c r="B16" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>132665513</v>
       </c>
       <c r="B17" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>

--- a/artfynd/S 1387-2022 artfynd.xlsx
+++ b/artfynd/S 1387-2022 artfynd.xlsx
@@ -2357,7 +2357,7 @@
         <v>132665500</v>
       </c>
       <c r="B16" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2477,7 +2477,7 @@
         <v>132665513</v>
       </c>
       <c r="B17" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
